--- a/Docs/QA-Testing/Bug_Report.xlsx
+++ b/Docs/QA-Testing/Bug_Report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Downloads/Online-Store/Docs/QA-Testing/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KiemChungPhanMem\Docs\QA-Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC9A1D03-1648-2642-9CF1-DD95BD4AB7F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E532889-CE28-4F86-B5DA-F3D6652004CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="173">
   <si>
     <t>Bug ID</t>
   </si>
@@ -523,18 +523,12 @@
     <t>1. Login customer1@email.com / 123 2. Vào /product/B0002 3. Thêm 1 sản phẩm vào cart 4. Click "Checkout" 5. Quan sát trang sau khi checkout</t>
   </si>
   <si>
-    <t>Checkout không thành công hoặc redirect sai. Phát hiện từ CodeceptJS TC_FE_CUS_CHK_01</t>
-  </si>
-  <si>
     <t>Subtotal = $40.00, Total = $40.00</t>
   </si>
   <si>
     <t>Subtotal = $40,160.00, Total = $40,160.00</t>
   </si>
   <si>
-    <t>Thêm quantity = 2 nhưng tính tiền sai rất lớn. Phát hiện từ CodeceptJS TC_FE_CUS_CART_01</t>
-  </si>
-  <si>
     <t>1. Login manager1@email.com / 123 2. Vào /seller/product 3. Click Edit sản phẩm 4. Điền Price = -50 5. Click Submit 6. Kiểm tra Network: PUT trả 400</t>
   </si>
   <si>
@@ -545,6 +539,12 @@
   </si>
   <si>
     <t>API đã fix (SCRUM-43/44). FE không hiển thị lỗi từ response. Phát hiện từ CodeceptJS TC_FE_MGR_03 + Network tab</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Retest không tái hiện / PASS khi chạy lại; không assign fixer. Không tính Open.</t>
   </si>
 </sst>
 </file>
@@ -980,22 +980,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.5" customWidth="1"/>
+    <col min="1" max="1" width="14.77734375" customWidth="1"/>
+    <col min="2" max="2" width="30.44140625" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="22.5" customWidth="1"/>
+    <col min="4" max="4" width="22.44140625" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
     <col min="7" max="7" width="30" customWidth="1"/>
-    <col min="8" max="8" width="15.1640625" customWidth="1"/>
+    <col min="8" max="8" width="15.109375" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="39.5" customWidth="1"/>
+    <col min="11" max="11" width="39.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1030,7 +1030,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" ht="60" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
@@ -1065,7 +1065,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" ht="45" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>17</v>
       </c>
@@ -1100,8 +1100,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:11" ht="45" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
         <v>49</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="K4" s="3"/>
     </row>
-    <row r="5" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>57</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" ht="45" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>62</v>
       </c>
@@ -1203,7 +1203,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="45" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>68</v>
       </c>
@@ -1238,7 +1238,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="60" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>72</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>75</v>
       </c>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="K9" s="3"/>
     </row>
-    <row r="10" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>78</v>
       </c>
@@ -1341,8 +1341,8 @@
         <v>81</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
         <v>82</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -1376,7 +1376,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="60" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>92</v>
       </c>
@@ -1411,7 +1411,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="85" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="75" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
         <v>98</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="68" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="60" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>106</v>
       </c>
@@ -1479,7 +1479,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="45" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>107</v>
       </c>
@@ -1512,7 +1512,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="51" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="60" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
         <v>108</v>
       </c>
@@ -1545,8 +1545,8 @@
         <v>142</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:11" ht="45" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
         <v>115</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -1580,8 +1580,8 @@
         <v>119</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="51" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
+    <row r="18" spans="1:11" ht="45" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
         <v>120</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -1615,8 +1615,8 @@
         <v>119</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
+    <row r="19" spans="1:11" ht="45" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
         <v>124</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -1650,8 +1650,8 @@
         <v>128</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="34" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
+    <row r="20" spans="1:11" ht="45" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
         <v>129</v>
       </c>
       <c r="B20" s="3" t="s">
@@ -1685,8 +1685,8 @@
         <v>133</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="102" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
+    <row r="21" spans="1:11" ht="90" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
         <v>145</v>
       </c>
       <c r="B21" s="3" t="s">
@@ -1720,8 +1720,8 @@
         <v>151</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="68" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
+    <row r="22" spans="1:11" ht="60" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
         <v>152</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -1737,10 +1737,10 @@
         <v>163</v>
       </c>
       <c r="F22" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>15</v>
@@ -1748,13 +1748,15 @@
       <c r="I22" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="J22" s="3"/>
+      <c r="J22" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="K22" s="3" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" ht="119" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="120" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
         <v>153</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -1781,13 +1783,15 @@
       <c r="I23" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="J23" s="3"/>
+      <c r="J23" s="3" t="s">
+        <v>171</v>
+      </c>
       <c r="K23" s="3" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" ht="85" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="75" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
         <v>154</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -1800,13 +1804,13 @@
         <v>18</v>
       </c>
       <c r="E24" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>171</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>22</v>
@@ -1818,7 +1822,7 @@
         <v>16</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -1831,83 +1835,83 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>39</v>
       </c>
